--- a/sample_data/demo_lista_materiales.xlsx
+++ b/sample_data/demo_lista_materiales.xlsx
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="F2" s="1" t="n">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -575,10 +575,10 @@
         </is>
       </c>
       <c r="F3" s="1" t="n">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -632,10 +632,10 @@
         </is>
       </c>
       <c r="F4" s="1" t="n">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="H4" t="n">
         <v>2</v>
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="F5" s="1" t="n">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="H5" t="n">
         <v>3</v>
@@ -746,10 +746,10 @@
         </is>
       </c>
       <c r="F6" s="1" t="n">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="H6" t="n">
         <v>4</v>
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="F7" s="1" t="n">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F8" s="1" t="n">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="F9" s="1" t="n">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
@@ -971,10 +971,10 @@
         </is>
       </c>
       <c r="F10" s="1" t="n">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="H10" t="n">
         <v>3</v>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="F11" s="1" t="n">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="F12" s="1" t="n">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="F13" s="1" t="n">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="H13" t="n">
         <v>2</v>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="F14" s="1" t="n">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="F15" s="1" t="n">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="F16" s="1" t="n">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="H16" t="n">
         <v>2</v>
@@ -1364,10 +1364,10 @@
         </is>
       </c>
       <c r="F17" s="1" t="n">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="F18" s="1" t="n">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="H18" t="n">
         <v>1</v>
@@ -1475,10 +1475,10 @@
         </is>
       </c>
       <c r="F19" s="1" t="n">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="F20" s="1" t="n">
-        <v>46215</v>
+        <v>46217</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46275</v>
+        <v>46277</v>
       </c>
       <c r="H20" t="n">
         <v>1</v>
